--- a/tfm_key_experiments_comparison_updated.xlsx
+++ b/tfm_key_experiments_comparison_updated.xlsx
@@ -9,18 +9,20 @@
   <sheets>
     <sheet name="Lectura_rapida" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stage1_TEST_interno" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Stage1_externo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Stage2_VALIDATION" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stage2_TEST_final" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Definiciones" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Stage1_VALIDATION" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Stage1_externo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stage2_VALIDATION" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Stage2_TEST_final" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Definiciones" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lectura_rapida'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stage1_TEST_interno'!$A$1:$AA$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stage1_externo'!$A$1:$U$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stage2_VALIDATION'!$A$1:$X$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Stage2_TEST_final'!$A$1:$W$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Definiciones'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stage1_TEST_interno'!$A$1:$AQ$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Stage1_VALIDATION'!$A$1:$AB$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stage1_externo'!$A$1:$W$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Stage2_VALIDATION'!$A$1:$X$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Stage2_TEST_final'!$A$1:$W$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Definiciones'!$A$1:$B$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -180,9 +182,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TFMTable2" displayName="TFMTable2" ref="A1:AA6" headerRowCount="1">
-  <autoFilter ref="A1:AA6"/>
-  <tableColumns count="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TFMTable2" displayName="TFMTable2" ref="A1:AQ6" headerRowCount="1">
+  <autoFilter ref="A1:AQ6"/>
+  <tableColumns count="43">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Experimento"/>
     <tableColumn id="3" name="Datos positivos"/>
@@ -191,62 +193,117 @@
     <tableColumn id="6" name="Grupo de comparabilidad"/>
     <tableColumn id="7" name="Configuración LR"/>
     <tableColumn id="8" name="Umbral"/>
-    <tableColumn id="9" name="N TEST"/>
-    <tableColumn id="10" name="No tos TEST"/>
-    <tableColumn id="11" name="Tos TEST"/>
-    <tableColumn id="12" name="Accuracy TEST"/>
-    <tableColumn id="13" name="Balanced accuracy TEST"/>
-    <tableColumn id="14" name="Sensibilidad / recall tos TEST"/>
-    <tableColumn id="15" name="Especificidad / recall no tos TEST"/>
-    <tableColumn id="16" name="Precisión tos TEST"/>
-    <tableColumn id="17" name="F1 tos TEST"/>
-    <tableColumn id="18" name="Macro-F1 TEST"/>
-    <tableColumn id="19" name="ROC-AUC TEST"/>
-    <tableColumn id="20" name="Recall toses CoughVID TEST"/>
-    <tableColumn id="21" name="Recall toses FSD50K TEST"/>
-    <tableColumn id="22" name="FP TEST"/>
-    <tableColumn id="23" name="FN TEST"/>
-    <tableColumn id="24" name="Macro-F1 OOF"/>
-    <tableColumn id="25" name="Macro-F1 VALIDATION"/>
-    <tableColumn id="26" name="Modelo KB"/>
-    <tableColumn id="27" name="Fuente"/>
+    <tableColumn id="9" name="N VALIDATION"/>
+    <tableColumn id="10" name="No tos VALIDATION"/>
+    <tableColumn id="11" name="Tos VALIDATION"/>
+    <tableColumn id="12" name="Accuracy VALIDATION"/>
+    <tableColumn id="13" name="Balanced accuracy VALIDATION"/>
+    <tableColumn id="14" name="Sensibilidad / recall tos VALIDATION"/>
+    <tableColumn id="15" name="Especificidad / recall no tos VALIDATION"/>
+    <tableColumn id="16" name="Precision tos VALIDATION"/>
+    <tableColumn id="17" name="F1 tos VALIDATION"/>
+    <tableColumn id="18" name="Macro-F1 VALIDATION"/>
+    <tableColumn id="19" name="ROC-AUC VALIDATION"/>
+    <tableColumn id="20" name="Recall toses CoughVID VALIDATION"/>
+    <tableColumn id="21" name="Recall toses FSD50K VALIDATION"/>
+    <tableColumn id="22" name="TN VALIDATION"/>
+    <tableColumn id="23" name="FP VALIDATION"/>
+    <tableColumn id="24" name="FN VALIDATION"/>
+    <tableColumn id="25" name="TP VALIDATION"/>
+    <tableColumn id="26" name="N TEST"/>
+    <tableColumn id="27" name="No tos TEST"/>
+    <tableColumn id="28" name="Tos TEST"/>
+    <tableColumn id="29" name="Accuracy TEST"/>
+    <tableColumn id="30" name="Balanced accuracy TEST"/>
+    <tableColumn id="31" name="Sensibilidad / recall tos TEST"/>
+    <tableColumn id="32" name="Especificidad / recall no tos TEST"/>
+    <tableColumn id="33" name="Precisión tos TEST"/>
+    <tableColumn id="34" name="F1 tos TEST"/>
+    <tableColumn id="35" name="Macro-F1 TEST"/>
+    <tableColumn id="36" name="ROC-AUC TEST"/>
+    <tableColumn id="37" name="Recall toses CoughVID TEST"/>
+    <tableColumn id="38" name="Recall toses FSD50K TEST"/>
+    <tableColumn id="39" name="FP TEST"/>
+    <tableColumn id="40" name="FN TEST"/>
+    <tableColumn id="41" name="Macro-F1 OOF"/>
+    <tableColumn id="42" name="Modelo KB"/>
+    <tableColumn id="43" name="Fuente"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TFMTable3" displayName="TFMTable3" ref="A1:U4" headerRowCount="1">
-  <autoFilter ref="A1:U4"/>
-  <tableColumns count="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TFMTable3" displayName="TFMTable3" ref="A1:AB6" headerRowCount="1">
+  <autoFilter ref="A1:AB6"/>
+  <tableColumns count="28">
     <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Modelo"/>
-    <tableColumn id="3" name="Protocolo"/>
-    <tableColumn id="4" name="Umbral"/>
-    <tableColumn id="5" name="N"/>
-    <tableColumn id="6" name="No tos"/>
-    <tableColumn id="7" name="Tos"/>
-    <tableColumn id="8" name="Accuracy"/>
-    <tableColumn id="9" name="Balanced accuracy"/>
-    <tableColumn id="10" name="Sensibilidad / recall tos"/>
-    <tableColumn id="11" name="Especificidad / recall no tos"/>
-    <tableColumn id="12" name="Precisión tos"/>
-    <tableColumn id="13" name="F1 tos"/>
-    <tableColumn id="14" name="Macro-F1"/>
-    <tableColumn id="15" name="ROC-AUC"/>
-    <tableColumn id="16" name="Average precision"/>
-    <tableColumn id="17" name="TN"/>
-    <tableColumn id="18" name="FP"/>
-    <tableColumn id="19" name="FN"/>
-    <tableColumn id="20" name="TP"/>
-    <tableColumn id="21" name="Fuente"/>
+    <tableColumn id="2" name="Experimento"/>
+    <tableColumn id="3" name="Datos positivos"/>
+    <tableColumn id="4" name="Augmentation en TRAIN"/>
+    <tableColumn id="5" name="Protocolo"/>
+    <tableColumn id="6" name="Grupo de comparabilidad"/>
+    <tableColumn id="7" name="Configuración LR"/>
+    <tableColumn id="8" name="Umbral"/>
+    <tableColumn id="9" name="N VALIDATION"/>
+    <tableColumn id="10" name="No tos VALIDATION"/>
+    <tableColumn id="11" name="Tos VALIDATION"/>
+    <tableColumn id="12" name="Accuracy VALIDATION"/>
+    <tableColumn id="13" name="Balanced accuracy VALIDATION"/>
+    <tableColumn id="14" name="Sensibilidad / recall tos VALIDATION"/>
+    <tableColumn id="15" name="Especificidad / recall no tos VALIDATION"/>
+    <tableColumn id="16" name="Precision tos VALIDATION"/>
+    <tableColumn id="17" name="F1 tos VALIDATION"/>
+    <tableColumn id="18" name="Macro-F1 VALIDATION"/>
+    <tableColumn id="19" name="ROC-AUC VALIDATION"/>
+    <tableColumn id="20" name="Recall toses CoughVID VALIDATION"/>
+    <tableColumn id="21" name="Recall toses FSD50K VALIDATION"/>
+    <tableColumn id="22" name="TN VALIDATION"/>
+    <tableColumn id="23" name="FP VALIDATION"/>
+    <tableColumn id="24" name="FN VALIDATION"/>
+    <tableColumn id="25" name="TP VALIDATION"/>
+    <tableColumn id="26" name="Macro-F1 OOF"/>
+    <tableColumn id="27" name="Modelo KB"/>
+    <tableColumn id="28" name="Fuente"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TFMTable4" displayName="TFMTable4" ref="A1:X12" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TFMTable4" displayName="TFMTable4" ref="A1:W4" headerRowCount="1">
+  <autoFilter ref="A1:W4"/>
+  <tableColumns count="23">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Modelo"/>
+    <tableColumn id="3" name="Protocolo"/>
+    <tableColumn id="4" name="Fecha evaluacion UTC"/>
+    <tableColumn id="5" name="SHA-256 metadatos"/>
+    <tableColumn id="6" name="Umbral"/>
+    <tableColumn id="7" name="N"/>
+    <tableColumn id="8" name="No tos"/>
+    <tableColumn id="9" name="Tos"/>
+    <tableColumn id="10" name="Accuracy"/>
+    <tableColumn id="11" name="Balanced accuracy"/>
+    <tableColumn id="12" name="Sensibilidad / recall tos"/>
+    <tableColumn id="13" name="Especificidad / recall no tos"/>
+    <tableColumn id="14" name="Precisión tos"/>
+    <tableColumn id="15" name="F1 tos"/>
+    <tableColumn id="16" name="Macro-F1"/>
+    <tableColumn id="17" name="ROC-AUC"/>
+    <tableColumn id="18" name="Average precision"/>
+    <tableColumn id="19" name="TN"/>
+    <tableColumn id="20" name="FP"/>
+    <tableColumn id="21" name="FN"/>
+    <tableColumn id="22" name="TP"/>
+    <tableColumn id="23" name="Fuente"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TFMTable5" displayName="TFMTable5" ref="A1:X12" headerRowCount="1">
   <autoFilter ref="A1:X12"/>
   <tableColumns count="24">
     <tableColumn id="1" name="ID"/>
@@ -278,8 +335,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TFMTable5" displayName="TFMTable5" ref="A1:W5" headerRowCount="1">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TFMTable6" displayName="TFMTable6" ref="A1:W5" headerRowCount="1">
   <autoFilter ref="A1:W5"/>
   <tableColumns count="23">
     <tableColumn id="1" name="ID"/>
@@ -310,8 +367,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TFMTable6" displayName="TFMTable6" ref="A1:B10" headerRowCount="1">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TFMTable7" displayName="TFMTable7" ref="A1:B10" headerRowCount="1">
   <autoFilter ref="A1:B10"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Concepto"/>
@@ -716,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -727,25 +784,41 @@
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="24" customWidth="1" min="30" max="30"/>
+    <col width="32" customWidth="1" min="31" max="31"/>
+    <col width="36" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="28" customWidth="1" min="37" max="37"/>
+    <col width="26" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="38" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -791,95 +864,175 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>N VALIDATION</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>No tos VALIDATION</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Tos VALIDATION</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy VALIDATION</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Balanced accuracy VALIDATION</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Sensibilidad / recall tos VALIDATION</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Especificidad / recall no tos VALIDATION</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Precision tos VALIDATION</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>F1 tos VALIDATION</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Macro-F1 VALIDATION</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>ROC-AUC VALIDATION</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Recall toses CoughVID VALIDATION</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Recall toses FSD50K VALIDATION</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>TN VALIDATION</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>FP VALIDATION</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>FN VALIDATION</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>TP VALIDATION</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
           <t>N TEST</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>No tos TEST</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>Tos TEST</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>Accuracy TEST</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>Balanced accuracy TEST</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>Sensibilidad / recall tos TEST</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>Especificidad / recall no tos TEST</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="AG1" s="2" t="inlineStr">
         <is>
           <t>Precisión tos TEST</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="AH1" s="2" t="inlineStr">
         <is>
           <t>F1 tos TEST</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="AI1" s="2" t="inlineStr">
         <is>
           <t>Macro-F1 TEST</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="AJ1" s="2" t="inlineStr">
         <is>
           <t>ROC-AUC TEST</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="AK1" s="2" t="inlineStr">
         <is>
           <t>Recall toses CoughVID TEST</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="AL1" s="2" t="inlineStr">
         <is>
           <t>Recall toses FSD50K TEST</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="AM1" s="2" t="inlineStr">
         <is>
           <t>FP TEST</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="AN1" s="2" t="inlineStr">
         <is>
           <t>FN TEST</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="AO1" s="2" t="inlineStr">
         <is>
           <t>Macro-F1 OOF</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>Macro-F1 VALIDATION</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AP1" s="2" t="inlineStr">
         <is>
           <t>Modelo KB</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AQ1" s="2" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
@@ -925,58 +1078,104 @@
         <v>0.5</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>423</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.9811205846528624</v>
+        <v>0.9810975609756096</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.9749348863638568</v>
+        <v>0.9772383355575368</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.9621749408983452</v>
+        <v>0.9692671394799054</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.9876948318293683</v>
-      </c>
-      <c r="P2" s="4" t="n">
-        <v>0.9644549763033176</v>
+        <v>0.9852095316351684</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.9579439252336448</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.9633136094674556</v>
+        <v>0.963572267920094</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.9753017411830922</v>
+        <v>0.9754049071177252</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.9984000372354972</v>
+        <v>0.9956292942184304</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>0.9621749408983452</v>
+        <v>0.9692671394799054</v>
       </c>
       <c r="U2" s="4" t="inlineStr"/>
       <c r="V2" s="3" t="n">
+        <v>1199</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>410</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>1642</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>1219</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>423</v>
+      </c>
+      <c r="AC2" s="4" t="n">
+        <v>0.9811205846528624</v>
+      </c>
+      <c r="AD2" s="4" t="n">
+        <v>0.9749348863638568</v>
+      </c>
+      <c r="AE2" s="4" t="n">
+        <v>0.9621749408983452</v>
+      </c>
+      <c r="AF2" s="4" t="n">
+        <v>0.9876948318293683</v>
+      </c>
+      <c r="AG2" s="4" t="n">
+        <v>0.9644549763033176</v>
+      </c>
+      <c r="AH2" s="4" t="n">
+        <v>0.9633136094674556</v>
+      </c>
+      <c r="AI2" s="4" t="n">
+        <v>0.9753017411830922</v>
+      </c>
+      <c r="AJ2" s="4" t="n">
+        <v>0.9984000372354972</v>
+      </c>
+      <c r="AK2" s="4" t="n">
+        <v>0.9621749408983452</v>
+      </c>
+      <c r="AL2" s="4" t="inlineStr"/>
+      <c r="AM2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="W2" s="3" t="n">
+      <c r="AN2" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="AO2" s="4" t="n">
         <v>0.9743136202185564</v>
       </c>
-      <c r="Y2" s="4" t="n">
-        <v>0.9754049071177252</v>
-      </c>
-      <c r="Z2" s="3" t="n">
+      <c r="AP2" s="3" t="n">
         <v>4.9970703125</v>
       </c>
-      <c r="AA2" s="3" t="inlineStr">
+      <c r="AQ2" s="3" t="inlineStr">
         <is>
           <t>results_stage1_cough_no_cough\mfcc117_lr_random\full\metrics_summary.csv</t>
         </is>
@@ -1022,60 +1221,108 @@
         <v>0.5</v>
       </c>
       <c r="I3" s="3" t="n">
+        <v>1709</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1246</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0.9713282621416032</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0.9599781937188204</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0.9352051835853132</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0.9847512038523274</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.9579646017699116</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0.946448087431694</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0.963435789620761</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0.9932553068306702</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0.9744186046511628</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0.4242424242424242</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>1227</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>433</v>
+      </c>
+      <c r="Z3" s="3" t="n">
         <v>1689</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="AA3" s="3" t="n">
         <v>1261</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="AB3" s="3" t="n">
         <v>428</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>0.9692125518058022</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>0.9608603170603364</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="AE3" s="4" t="n">
         <v>0.9439252336448598</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="AF3" s="4" t="n">
         <v>0.9777954004758128</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>0.9351851851851852</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="AH3" s="4" t="n">
         <v>0.9395348837209302</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="AI3" s="4" t="n">
         <v>0.9594417865784952</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>0.9935020418448496</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="AK3" s="4" t="n">
         <v>0.977667493796526</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="AL3" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="AM3" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="AN3" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AO3" s="4" t="n">
         <v>0.9544231772476612</v>
       </c>
-      <c r="Y3" s="4" t="n">
-        <v>0.963435789620761</v>
-      </c>
-      <c r="Z3" s="3" t="n">
+      <c r="AP3" s="3" t="n">
         <v>4.9970703125</v>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AQ3" s="3" t="inlineStr">
         <is>
           <t>results_stage1_cough_no_cough\mfcc117_lr_fsd50k_cough_segments_random\full\metrics_summary.csv</t>
         </is>
@@ -1121,60 +1368,108 @@
         <v>0.5</v>
       </c>
       <c r="I4" s="3" t="n">
+        <v>1709</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1246</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0.9379754242246928</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0.9493203304570306</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0.9740820734341252</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0.9245585874799358</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.8275229357798165</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0.8948412698412699</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>0.9254289336758216</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0.9900120991925784</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0.9976744186046512</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1152</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>451</v>
+      </c>
+      <c r="Z4" s="3" t="n">
         <v>1689</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="AA4" s="3" t="n">
         <v>1261</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="AB4" s="3" t="n">
         <v>428</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>0.9396092362344582</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="AD4" s="4" t="n">
         <v>0.9533821992633054</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="AE4" s="4" t="n">
         <v>0.9813084112149532</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="AF4" s="4" t="n">
         <v>0.9254559873116576</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="AG4" s="4" t="n">
         <v>0.8171206225680934</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="AH4" s="4" t="n">
         <v>0.89171974522293</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="AI4" s="4" t="n">
         <v>0.924923912020332</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="AJ4" s="4" t="n">
         <v>0.9917307136451564</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="AK4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="AL4" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="AM4" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="AN4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="AO4" s="4" t="n">
         <v>0.9221817270697834</v>
       </c>
-      <c r="Y4" s="4" t="n">
-        <v>0.9254289336758216</v>
-      </c>
-      <c r="Z4" s="3" t="n">
+      <c r="AP4" s="3" t="n">
         <v>4.9970703125</v>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="AQ4" s="3" t="inlineStr">
         <is>
           <t>results_stage1_cough_no_cough\mfcc117_lr_fsd50k_cough_segments_audio_aug_random\full\metrics_summary.csv</t>
         </is>
@@ -1220,60 +1515,108 @@
         <v>0.5</v>
       </c>
       <c r="I5" s="3" t="n">
+        <v>1709</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>1246</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.946167349327092</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.9515451604963095</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.9632829373650108</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0.9398073836276084</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.8560460652591171</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0.9065040650406504</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0.9343531007208182</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0.9884971000072804</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0.9953488372093025</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>1171</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>446</v>
+      </c>
+      <c r="Z5" s="3" t="n">
         <v>1689</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="AA5" s="3" t="n">
         <v>1261</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="AB5" s="3" t="n">
         <v>428</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="AC5" s="4" t="n">
         <v>0.9561870929544108</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="AD5" s="4" t="n">
         <v>0.9613976446522934</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="AE5" s="4" t="n">
         <v>0.97196261682243</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="AF5" s="4" t="n">
         <v>0.950832672482157</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="AG5" s="4" t="n">
         <v>0.8702928870292888</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="AH5" s="4" t="n">
         <v>0.9183222958057397</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="AI5" s="4" t="n">
         <v>0.9441935103624168</v>
       </c>
-      <c r="S5" s="4" t="n">
+      <c r="AJ5" s="4" t="n">
         <v>0.9899297397852173</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="AK5" s="4" t="n">
         <v>0.9975186104218362</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="AL5" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="AM5" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="AN5" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="X5" s="4" t="n">
+      <c r="AO5" s="4" t="n">
         <v>0.9290377500221316</v>
       </c>
-      <c r="Y5" s="4" t="n">
-        <v>0.9343531007208182</v>
-      </c>
-      <c r="Z5" s="3" t="n">
+      <c r="AP5" s="3" t="n">
         <v>4.9970703125</v>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AQ5" s="3" t="inlineStr">
         <is>
           <t>results_stage1_cough_no_cough\mfcc117_lr_fsd50k_cough_segments_noise_aug_random\full\metrics_summary.csv</t>
         </is>
@@ -1319,65 +1662,113 @@
         <v>0.5</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>1705</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1212</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>493</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.960117302052786</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.9538974688543904</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.9391480730223124</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0.9686468646864688</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0.9241516966067864</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0.93158953722334</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0.9517219209295508</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0.9865208630396508</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0.9848156182212582</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>1174</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="Z6" s="3" t="n">
         <v>1486</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="AA6" s="3" t="n">
         <v>1216</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="AB6" s="3" t="n">
         <v>270</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="AC6" s="4" t="n">
         <v>0.9582772543741588</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="AD6" s="4" t="n">
         <v>0.9500152290448344</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="AE6" s="4" t="n">
         <v>0.937037037037037</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="AF6" s="4" t="n">
         <v>0.9629934210526316</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="AG6" s="4" t="n">
         <v>0.8489932885906041</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="AH6" s="4" t="n">
         <v>0.8908450704225352</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="AI6" s="4" t="n">
         <v>0.932527360502449</v>
       </c>
-      <c r="S6" s="4" t="n">
+      <c r="AJ6" s="4" t="n">
         <v>0.9911245126705652</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="AK6" s="4" t="n">
         <v>0.937037037037037</v>
       </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="3" t="n">
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="AN6" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="X6" s="4" t="n">
+      <c r="AO6" s="4" t="n">
         <v>0.9561967063357104</v>
       </c>
-      <c r="Y6" s="4" t="n">
-        <v>0.9517219209295508</v>
-      </c>
-      <c r="Z6" s="3" t="n">
+      <c r="AP6" s="3" t="n">
         <v>4.9970703125</v>
       </c>
-      <c r="AA6" s="3" t="inlineStr">
+      <c r="AQ6" s="3" t="inlineStr">
         <is>
           <t>results_stage1_cough_no_cough\mfcc117_lr_fsd50k_cough_segments_audio_quality_poor\full\metrics_summary.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA6"/>
+  <autoFilter ref="A1:AQ6"/>
   <conditionalFormatting sqref="H2:H6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -1438,7 +1829,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1450,7 +1841,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -1462,7 +1853,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="S2:S6">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -1474,7 +1865,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S6">
+  <conditionalFormatting sqref="T2:T6">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -1486,7 +1877,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T6">
+  <conditionalFormatting sqref="U2:U6">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -1498,7 +1889,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U6">
+  <conditionalFormatting sqref="AC2:AC6">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -1510,7 +1901,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X6">
+  <conditionalFormatting sqref="AD2:AD6">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -1522,8 +1913,104 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y6">
+  <conditionalFormatting sqref="AE2:AE6">
     <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF2:AF6">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG2:AG6">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH2:AH6">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI2:AI6">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ2:AJ6">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK2:AK6">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL2:AL6">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO2:AO6">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1547,30 +2034,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="38" customWidth="1" min="21" max="21"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -1581,100 +2075,135 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Modelo</t>
+          <t>Experimento</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Datos positivos</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Augmentation en TRAIN</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Protocolo</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Grupo de comparabilidad</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Configuración LR</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Umbral</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>No tos</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Tos</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>Balanced accuracy</t>
+          <t>N VALIDATION</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>Sensibilidad / recall tos</t>
+          <t>No tos VALIDATION</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>Especificidad / recall no tos</t>
+          <t>Tos VALIDATION</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>Precisión tos</t>
+          <t>Accuracy VALIDATION</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>F1 tos</t>
+          <t>Balanced accuracy VALIDATION</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>Macro-F1</t>
+          <t>Sensibilidad / recall tos VALIDATION</t>
         </is>
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
-          <t>ROC-AUC</t>
+          <t>Especificidad / recall no tos VALIDATION</t>
         </is>
       </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
-          <t>Average precision</t>
+          <t>Precision tos VALIDATION</t>
         </is>
       </c>
       <c r="Q1" s="2" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>F1 tos VALIDATION</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>Macro-F1 VALIDATION</t>
         </is>
       </c>
       <c r="S1" s="2" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>ROC-AUC VALIDATION</t>
         </is>
       </c>
       <c r="T1" s="2" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>Recall toses CoughVID VALIDATION</t>
         </is>
       </c>
       <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Recall toses FSD50K VALIDATION</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>TN VALIDATION</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>FP VALIDATION</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>FN VALIDATION</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>TP VALIDATION</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>Macro-F1 OOF</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>Modelo KB</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
@@ -1683,225 +2212,514 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>EXT-01</t>
+          <t>S1-LR-01</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Sin augmentation</t>
+          <t>MFCC117 + LR; CoughVID como clase positiva</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Validación piloto externa; mismas 58 muestras; sin ajuste de modelo ni umbral</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
+          <t>CoughVID</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Split aleatorio agrupado</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>A: referencia anterior; distinto conjunto positivo</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>lr__C0p3__l1__weight_none</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>0.7241379310344828</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>0.7678812415654521</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>0.6410256410256411</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0.8947368421052632</v>
+      <c r="I2" s="3" t="n">
+        <v>1640</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>1217</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>423</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.925925925925926</v>
+        <v>0.9810975609756096</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.9772383355575368</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.7187878787878788</v>
+        <v>0.9692671394799054</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.8771929824561404</v>
-      </c>
-      <c r="P2" s="4" t="n">
-        <v>0.9454144627643296</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="T2" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>results_external_validation\stage1_mfcc117_lr_fsd50k_cough_segments\external_validation_metrics.csv</t>
+        <v>0.9852095316351684</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.9579439252336448</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0.963572267920094</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>0.9754049071177252</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>0.9956292942184304</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>0.9692671394799054</v>
+      </c>
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="3" t="n">
+        <v>1199</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>410</v>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <v>0.9743136202185564</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>4.9970703125</v>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>results_stage1_cough_no_cough\mfcc117_lr_random\full\metrics_summary.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>EXT-02</t>
+          <t>S1-LR-02</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Pitch + ruido</t>
+          <t>MFCC117 + LR; CoughVID + FSD50K</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Validación piloto externa; mismas 58 muestras; sin ajuste de modelo ni umbral</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
+          <t>CoughVID + toses FSD50K revisadas y segmentadas</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Split aleatorio agrupado</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>B: comparación principal; mismo TEST que S1-LR-03/04</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>lr__C0p3__l1__weight_none</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="F3" s="3" t="n">
+      <c r="I3" s="3" t="n">
+        <v>1709</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1246</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0.9713282621416032</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0.9599781937188204</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0.9352051835853132</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0.9847512038523274</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.9579646017699116</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0.946448087431694</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0.963435789620761</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0.9932553068306702</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0.9744186046511628</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0.4242424242424242</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>1227</v>
+      </c>
+      <c r="W3" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0.7586206896551724</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0.6855600539811066</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>0.8974358974358975</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0.4736842105263157</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>0.6979166666666667</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>0.8272604588394062</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0.9162084796763812</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>results_external_validation\stage1_mfcc117_lr_fsd50k_cough_segments_audio_aug\external_validation_metrics.csv</t>
+      <c r="X3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>433</v>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>0.9544231772476612</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>4.9970703125</v>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>results_stage1_cough_no_cough\mfcc117_lr_fsd50k_cough_segments_random\full\metrics_summary.csv</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>EXT-03</t>
+          <t>S1-LR-03</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Solo ruido</t>
+          <t>MFCC117 + LR; augmentation pitch + ruido</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Validación piloto externa; mismas 58 muestras; sin ajuste de modelo ni umbral</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
+          <t>CoughVID + toses FSD50K revisadas y segmentadas</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2 variantes/tos TRAIN: pitch ±1.5 o ruido moderado/alto</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Split aleatorio agrupado; OOF/VAL/TEST solo originales</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>B: comparación principal; mismo TEST que S1-LR-02/04</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>lr__C0p3__l1__weight_none</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0.7758620689655172</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0.7253711201079622</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0.8717948717948718</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0.5789473684210527</v>
+      <c r="I4" s="3" t="n">
+        <v>1709</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1246</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>463</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.9379754242246928</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.8395061728395061</v>
+        <v>0.9493203304570306</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.7340388007054673</v>
+        <v>0.9740820734341252</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.8272604588394062</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0.9168399484909202</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>results_external_validation\stage1_mfcc117_lr_fsd50k_cough_segments_noise_aug\external_validation_metrics.csv</t>
+        <v>0.9245585874799358</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.8275229357798165</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0.8948412698412699</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>0.9254289336758216</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0.9900120991925784</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0.9976744186046512</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1152</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>451</v>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <v>0.9221817270697834</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>4.9970703125</v>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>results_stage1_cough_no_cough\mfcc117_lr_fsd50k_cough_segments_audio_aug_random\full\metrics_summary.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>S1-LR-04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>MFCC117 + LR; augmentation solo ruido</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>CoughVID + toses FSD50K revisadas y segmentadas</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1 variante/tos TRAIN: mezcla a 10 o 20 dB SNR</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Split aleatorio agrupado; OOF/VAL/TEST solo originales</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>B: comparación principal; mismo TEST que S1-LR-02/03</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>lr__C0p3__l1__weight_none</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1709</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>1246</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.946167349327092</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.9515451604963095</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.9632829373650108</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0.9398073836276084</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.8560460652591171</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0.9065040650406504</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0.9343531007208182</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0.9884971000072804</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0.9953488372093025</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>1171</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>446</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>0.9290377500221316</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>4.9970703125</v>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>results_stage1_cough_no_cough\mfcc117_lr_fsd50k_cough_segments_noise_aug_random\full\metrics_summary.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>S1-LR-05</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>MFCC117 + LR; stress test de calidad poor</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>TRAIN/VAL: CoughVID + FSD50K; TEST: CoughVID poor</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Todas las toses CoughVID poor reservadas en TEST</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>C: análisis secundario de robustez; TEST diferente</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>lr__C0p3__l1__weight_none</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1705</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1212</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>493</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.960117302052786</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.9538974688543904</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.9391480730223124</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0.9686468646864688</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0.9241516966067864</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0.93158953722334</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0.9517219209295508</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0.9865208630396508</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0.9848156182212582</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>1174</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="Z6" s="4" t="n">
+        <v>0.9561967063357104</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>4.9970703125</v>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>results_stage1_cough_no_cough\mfcc117_lr_fsd50k_cough_segments_audio_quality_poor\full\metrics_summary.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U4"/>
-  <conditionalFormatting sqref="D2:D4">
+  <autoFilter ref="A1:AB6"/>
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1913,7 +2731,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H4">
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1925,7 +2743,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I4">
+  <conditionalFormatting sqref="M2:M6">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1937,7 +2755,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J4">
+  <conditionalFormatting sqref="N2:N6">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1949,7 +2767,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K4">
+  <conditionalFormatting sqref="O2:O6">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1961,7 +2779,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L4">
+  <conditionalFormatting sqref="Q2:Q6">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1973,7 +2791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -1985,7 +2803,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="S2:S6">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -1997,7 +2815,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O4">
+  <conditionalFormatting sqref="T2:T6">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2009,8 +2827,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
+  <conditionalFormatting sqref="U2:U6">
     <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z6">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2029,6 +2859,535 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="38" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Protocolo</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Fecha evaluacion UTC</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 metadatos</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Umbral</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>No tos</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Tos</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Balanced accuracy</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Sensibilidad / recall tos</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Especificidad / recall no tos</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Precisión tos</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>F1 tos</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Macro-F1</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Average precision</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>EXT-01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Sin augmentation</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Evaluacion externa exploratoria post hoc; mismas 62 muestras; sin ajuste de modelo ni umbral</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-05T15:55:53.277647+00:00</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>6caf192fe582e2db12f1184e2540c9cff48f7b1e200cab6a0d860337c5c249f1</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0.7816492450638792</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>0.6585365853658537</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0.9310344827586208</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0.7375661375661375</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0.8792102206736353</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>0.9437790624697324</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>results_external_validation\stage1_mfcc117_lr_fsd50k_cough_segments\external_validation_metrics.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>EXT-02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Pitch + ruido</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Evaluacion externa exploratoria post hoc; mismas 62 muestras; sin ajuste de modelo ni umbral</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-05T15:58:08.322752+00:00</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>6caf192fe582e2db12f1184e2540c9cff48f7b1e200cab6a0d860337c5c249f1</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0.7580645161290323</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.68931475029036</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0.902439024390244</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0.4761904761904761</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0.8314606741573034</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0.7014446227929374</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0.8281068524970965</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0.9129469578240964</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>results_external_validation\stage1_mfcc117_lr_fsd50k_cough_segments_audio_aug\external_validation_metrics.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>EXT-03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Solo ruido</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Evaluacion externa exploratoria post hoc; mismas 62 muestras; sin ajuste de modelo ni umbral</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-05T15:58:54.024174+00:00</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>6caf192fe582e2db12f1184e2540c9cff48f7b1e200cab6a0d860337c5c249f1</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0.7247386759581882</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0.7343941248470012</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0.8315911730545877</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>0.9166671916925776</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>results_external_validation\stage1_mfcc117_lr_fsd50k_cough_segments_noise_aug\external_validation_metrics.csv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:W4"/>
+  <conditionalFormatting sqref="F2:F4">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J4">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K4">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M4">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N4">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O4">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P4">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q4">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R4">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3338,7 +4697,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3942,7 +5301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4071,7 +5430,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Piloto con 58 muestras recopiladas; no debe presentarse como estimación clínica ni usarse para reajustar el modelo retrospectivamente.</t>
+          <t>Evaluacion exploratoria con 62 muestras; no debe presentarse como estimacion clinica ni usarse para reajustar el modelo retrospectivamente.</t>
         </is>
       </c>
     </row>
